--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -18,9 +18,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,21 +29,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,27 +55,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22.36328125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -556,19 +531,6 @@
       </c>
       <c r="C9" t="n">
         <v>1693.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>88.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -638,6 +600,27 @@
       <c r="A8" t="inlineStr">
         <is>
           <t>AMD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GOOG.TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AMZN.TO</t>
         </is>
       </c>
     </row>
@@ -655,15 +638,14 @@
   <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="9.54296875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.08984375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
     <col width="10.7265625" customWidth="1" min="2" max="2"/>
-    <col width="8.81640625" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="10.08984375" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="9.90625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="8.81640625" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="10.08984375" bestFit="1" customWidth="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.5" customHeight="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>date</t>
         </is>
@@ -673,7 +655,7 @@
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>action</t>
         </is>
@@ -690,1514 +672,1514 @@
       </c>
     </row>
     <row r="2" ht="14.5" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>45656</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>33.73</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="E2" t="n">
         <v>12788.62</v>
       </c>
     </row>
     <row r="3" ht="14.5" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>45659</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>34.02</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" t="n">
         <v>9.65</v>
       </c>
     </row>
     <row r="4" ht="14.5" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>45659</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>33.9</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="5" ht="14.5" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>45664</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>33.95</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" t="n">
         <v>33.95</v>
       </c>
     </row>
     <row r="6" ht="14.5" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>45667</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>33.52</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" t="n">
         <v>1005.6</v>
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>45677</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>34.72</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" t="n">
         <v>694.4</v>
       </c>
     </row>
     <row r="8" ht="14.5" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>45681</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>34.91</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" t="n">
         <v>349.1</v>
       </c>
     </row>
     <row r="9" ht="14.5" customHeight="1">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>45685</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>34.86</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" t="n">
         <v>11.84</v>
       </c>
     </row>
     <row r="10" ht="14.5" customHeight="1">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>45686</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>34.8</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" t="n">
         <v>348</v>
       </c>
     </row>
     <row r="11" ht="14.5" customHeight="1">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45712</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>34.64</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" t="n">
         <v>866</v>
       </c>
     </row>
     <row r="12" ht="14.5" customHeight="1">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>45719</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>34.91</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" t="n">
         <v>349.1</v>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>45720</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>34.15</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" t="n">
         <v>819.6</v>
       </c>
     </row>
     <row r="14" ht="14.5" customHeight="1">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>45720</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>NVDA.TO</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>26.05</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" t="n">
         <v>104.2</v>
       </c>
     </row>
     <row r="15" ht="14.5" customHeight="1">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>45722</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>34.05</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" t="n">
         <v>340.4</v>
       </c>
     </row>
     <row r="16" ht="14.5" customHeight="1">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>45722</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>NVDA.TO</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>25.97</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" t="n">
         <v>363.58</v>
       </c>
     </row>
     <row r="17" ht="14.5" customHeight="1">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>45726</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>33.82</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" t="n">
         <v>202.92</v>
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>45726</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>NVDA.TO</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>24.99</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" t="n">
         <v>199.92</v>
       </c>
     </row>
     <row r="19" ht="14.5" customHeight="1">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>45729</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>33.54</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" t="n">
         <v>16367.52</v>
       </c>
     </row>
     <row r="20" ht="14.5" customHeight="1">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>45751</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>NVDA.TO</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>25.78</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" t="n">
         <v>670.28</v>
       </c>
     </row>
     <row r="21" ht="14.5" customHeight="1">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>45763</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>NVDA.TO</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>24.59</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" t="n">
         <v>245.9</v>
       </c>
     </row>
     <row r="22" ht="14.5" customHeight="1">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>45777</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>32.52</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" t="n">
         <v>325.2</v>
       </c>
     </row>
     <row r="23" ht="14.5" customHeight="1">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>45778</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>32.95</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" t="n">
         <v>329.5</v>
       </c>
     </row>
     <row r="24" ht="14.5" customHeight="1">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>45778</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>NVDA.TO</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>25.84</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" t="n">
         <v>258.4</v>
       </c>
     </row>
     <row r="25" ht="14.5" customHeight="1">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>45779</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>29.58</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" t="n">
         <v>591.6</v>
       </c>
     </row>
     <row r="26" ht="14.5" customHeight="1">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>33.3</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" t="n">
         <v>832.5</v>
       </c>
     </row>
     <row r="27" ht="14.5" customHeight="1">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>29.01</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" t="n">
         <v>290.1</v>
       </c>
     </row>
     <row r="28" ht="14.5" customHeight="1">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>45783</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>33.27</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" t="n">
         <v>831.75</v>
       </c>
     </row>
     <row r="29" ht="14.5" customHeight="1">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>28.24</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" t="n">
         <v>282.4</v>
       </c>
     </row>
     <row r="30" ht="14.5" customHeight="1">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45800</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>28.34</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" t="n">
         <v>1.27</v>
       </c>
     </row>
     <row r="31" ht="14.5" customHeight="1">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45807</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>28.87</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" t="n">
         <v>606.27</v>
       </c>
     </row>
     <row r="32" ht="14.5" customHeight="1">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45813</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>25.28</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" t="n">
         <v>505.6</v>
       </c>
     </row>
     <row r="33" ht="14.5" customHeight="1">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45821</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>34.78</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E33" t="n">
         <v>4104.04</v>
       </c>
     </row>
     <row r="34" ht="14.5" customHeight="1">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45821</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>28.46</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E34" t="n">
         <v>853.8</v>
       </c>
     </row>
     <row r="35" ht="14.5" customHeight="1">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45832</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>35.23</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" t="n">
         <v>1409.2</v>
       </c>
     </row>
     <row r="36" ht="14.5" customHeight="1">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45838</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>28.48</v>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" t="n">
         <v>1139.2</v>
       </c>
     </row>
     <row r="37" ht="14.5" customHeight="1">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45838</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>29.85</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" t="n">
         <v>895.5</v>
       </c>
     </row>
     <row r="38" ht="14.5" customHeight="1">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45840</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>35.53</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E38" t="n">
         <v>1421.2</v>
       </c>
     </row>
     <row r="39" ht="14.5" customHeight="1">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45840</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>27.55</v>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E39" t="n">
         <v>826.5</v>
       </c>
     </row>
     <row r="40" ht="14.5" customHeight="1">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45840</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="n">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>30.31</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" t="n">
         <v>606.2</v>
       </c>
     </row>
     <row r="41" ht="14.5" customHeight="1">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45845</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>26.29</v>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E41" t="n">
         <v>499.51</v>
       </c>
     </row>
     <row r="42" ht="14.5" customHeight="1">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45862</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>36.4</v>
       </c>
-      <c r="E42" s="7" t="n">
+      <c r="E42" t="n">
         <v>728</v>
       </c>
     </row>
     <row r="43" ht="14.5" customHeight="1">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45862</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>27.03</v>
       </c>
-      <c r="E43" s="7" t="n">
+      <c r="E43" t="n">
         <v>540.6</v>
       </c>
     </row>
     <row r="44" ht="14.5" customHeight="1">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45862</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>31.06</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" t="n">
         <v>621.2</v>
       </c>
     </row>
     <row r="45" ht="14.5" customHeight="1">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45866</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="n">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>29.24</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" t="n">
         <v>584.8</v>
       </c>
     </row>
     <row r="46" ht="14.5" customHeight="1">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45870</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>35.74</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E46" t="n">
         <v>2144.4</v>
       </c>
     </row>
     <row r="47" ht="14.5" customHeight="1">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="n">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>27.26</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E47" t="n">
         <v>517.9400000000001</v>
       </c>
     </row>
     <row r="48" ht="14.5" customHeight="1">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45870</v>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="n">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>29.38</v>
       </c>
-      <c r="E48" s="7" t="n">
+      <c r="E48" t="n">
         <v>881.4</v>
       </c>
     </row>
     <row r="49" ht="14.5" customHeight="1">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45870</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>AMZN.TO</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="n">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>25.3</v>
       </c>
-      <c r="E49" s="7" t="n">
+      <c r="E49" t="n">
         <v>2530</v>
       </c>
     </row>
     <row r="50" ht="14.5" customHeight="1">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45871</v>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>XEQT.TO</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>XEQT.TO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>36.58</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E50" t="n">
         <v>1097.4</v>
       </c>
     </row>
     <row r="51" ht="14.5" customHeight="1">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45876</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="n">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>31.46</v>
       </c>
-      <c r="E51" s="7" t="n">
+      <c r="E51" t="n">
         <v>629.2</v>
       </c>
     </row>
     <row r="52" ht="14.5" customHeight="1">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45876</v>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>AMZN.TO</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="n">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>26.32</v>
       </c>
-      <c r="E52" s="7" t="n">
+      <c r="E52" t="n">
         <v>526.4</v>
       </c>
     </row>
     <row r="53" ht="14.5" customHeight="1">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45876</v>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>INTC.TO</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="n">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>11.41</v>
       </c>
-      <c r="E53" s="7" t="n">
+      <c r="E53" t="n">
         <v>2282</v>
       </c>
     </row>
     <row r="54" ht="14.5" customHeight="1">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45876</v>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>MSFT.TO</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="n">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>37.84</v>
       </c>
-      <c r="E54" s="7" t="n">
+      <c r="E54" t="n">
         <v>3784</v>
       </c>
     </row>
     <row r="55" ht="14.5" customHeight="1">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45877</v>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="n">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>29.32</v>
       </c>
-      <c r="E55" s="7" t="n">
+      <c r="E55" t="n">
         <v>1172.8</v>
       </c>
     </row>
     <row r="56" ht="14.5" customHeight="1">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45880</v>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="n">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>30.37</v>
       </c>
-      <c r="E56" s="7" t="n">
+      <c r="E56" t="n">
         <v>607.4</v>
       </c>
     </row>
     <row r="57" ht="14.5" customHeight="1">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45880</v>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>INTC.TO</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>11.96</v>
       </c>
-      <c r="E57" s="7" t="n">
+      <c r="E57" t="n">
         <v>239.2</v>
       </c>
     </row>
     <row r="58" ht="14.5" customHeight="1">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45884</v>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="n">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>29.37</v>
       </c>
-      <c r="E58" s="7" t="n">
+      <c r="E58" t="n">
         <v>1468.5</v>
       </c>
     </row>
     <row r="59" ht="14.5" customHeight="1">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45888</v>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>NVDA.TO</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="n">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>40.45</v>
       </c>
-      <c r="E59" s="7" t="n">
+      <c r="E59" t="n">
         <v>2831.5</v>
       </c>
     </row>
     <row r="60" ht="14.5" customHeight="1">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45888</v>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="n">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
         <v>29.32</v>
       </c>
-      <c r="E60" s="7" t="n">
+      <c r="E60" t="n">
         <v>175.92</v>
       </c>
     </row>
     <row r="61" ht="14.5" customHeight="1">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45889</v>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>NVDA.TO</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="n">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
         <v>38.88</v>
       </c>
-      <c r="E61" s="7" t="n">
+      <c r="E61" t="n">
         <v>777.6</v>
       </c>
     </row>
     <row r="62" ht="14.5" customHeight="1">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>45889</v>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="n">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>28.16</v>
       </c>
-      <c r="E62" s="7" t="n">
+      <c r="E62" t="n">
         <v>478.72</v>
       </c>
     </row>
     <row r="63" ht="14.5" customHeight="1">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>45889</v>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>AMZN.TO</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="n">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>26</v>
       </c>
-      <c r="E63" s="7" t="n">
+      <c r="E63" t="n">
         <v>1040</v>
       </c>
     </row>
     <row r="64" ht="14.5" customHeight="1">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>45889</v>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>INTC.TO</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="n">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>13.56</v>
       </c>
-      <c r="E64" s="7" t="n">
+      <c r="E64" t="n">
         <v>271.2</v>
       </c>
     </row>
     <row r="65" ht="14.5" customHeight="1">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>45890</v>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="n">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>29.92</v>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E65" t="n">
         <v>897.6</v>
       </c>
     </row>
     <row r="66" ht="14.5" customHeight="1">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>45890</v>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="n">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
         <v>32.39</v>
       </c>
-      <c r="E66" s="7" t="n">
+      <c r="E66" t="n">
         <v>0.06</v>
       </c>
     </row>
     <row r="67" ht="14.5" customHeight="1">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>45890</v>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>AAPL.TO</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="n">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>32.39</v>
       </c>
-      <c r="E67" s="7" t="n">
+      <c r="E67" t="n">
         <v>0.92</v>
       </c>
     </row>
     <row r="68" ht="14.5" customHeight="1">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>45891</v>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>INTC.TO</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="n">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
         <v>14.11</v>
       </c>
-      <c r="E68" s="7" t="n">
+      <c r="E68" t="n">
         <v>423.3</v>
       </c>
     </row>
     <row r="69" ht="14.5" customHeight="1">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>45891</v>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>MSFT.TO</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="n">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>36.7</v>
       </c>
-      <c r="E69" s="7" t="n">
+      <c r="E69" t="n">
         <v>1284.5</v>
       </c>
     </row>
     <row r="70" ht="14.5" customHeight="1">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>45894</v>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="n">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
         <v>30.63</v>
       </c>
-      <c r="E70" s="7" t="n">
+      <c r="E70" t="n">
         <v>612.6</v>
       </c>
     </row>
     <row r="71" ht="14.5" customHeight="1">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>45894</v>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>TSLA.TO</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="n">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
         <v>30.98</v>
       </c>
-      <c r="E71" s="7" t="n">
+      <c r="E71" t="n">
         <v>619.6</v>
       </c>
     </row>
     <row r="72" ht="14.5" customHeight="1">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>45894</v>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>INTC.TO</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="n">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>14.45</v>
       </c>
-      <c r="E72" s="7" t="n">
+      <c r="E72" t="n">
         <v>433.5</v>
       </c>
     </row>
     <row r="73" ht="14.5" customHeight="1">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>45895</v>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>GOOG.TO</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="n">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
         <v>33.87</v>
       </c>
-      <c r="E73" s="7" t="n">
+      <c r="E73" t="n">
         <v>1693.5</v>
       </c>
     </row>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -17,9 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="340" yWindow="340" windowWidth="14400" windowHeight="8170" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="340" yWindow="340" windowWidth="14400" windowHeight="8170" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="owned stocks" sheetId="1" state="visible" r:id="rId1"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>INTC.TO</t>
+          <t>INTC.NE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>INTC.TO</t>
+          <t>INTC.NE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>INTC.TO</t>
+          <t>INTC.NE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>INTC.TO</t>
+          <t>INTC.NE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>INTC.TO</t>
+          <t>INTC.NE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
